--- a/files/ALPHADHABI_Valuation_Model_10-07-2026_public.xlsx
+++ b/files/ALPHADHABI_Valuation_Model_10-07-2026_public.xlsx
@@ -24,6 +24,7 @@
     <sheet name="14_Sweep_Gate" sheetId="14" state="visible" r:id="rId16"/>
     <sheet name="15_Ledger" sheetId="15" state="visible" r:id="rId17"/>
     <sheet name="16_Experts" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="17_Ratios" sheetId="17" state="visible" r:id="rId19"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="490">
   <si>
     <t xml:space="preserve">Alpha Dhabi Holding PJSC (ADX: ALPHADHABI) — Independent Valuation Study</t>
   </si>
@@ -241,6 +242,30 @@
     <t xml:space="preserve">UAE long-run nominal proxy; sensitised 2.0–4.0%</t>
   </si>
   <si>
+    <t xml:space="preserve">Parent book — owners FY25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audited FY25 FS: equity attributable to owners</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carried book of the 5 marked stakes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparer allocation (Driver Ledger); NAV total independent of split</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trojan 100% — buyer-outlay basis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADQ 49% deal: ADH FY24 CF 4,997mn (ADQ-side ~5,043) → /0.49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trojan 100% — seller-note basis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADH FY24 disposal note: consideration 3,562mn (+1,456 NCI) → /0.49</t>
+  </si>
+  <si>
     <t xml:space="preserve">Holdco discount (central)</t>
   </si>
   <si>
@@ -547,6 +572,9 @@
     <t xml:space="preserve">SOTP / NAV — attributable, market marks (AED bn)</t>
   </si>
   <si>
+    <t xml:space="preserve">Every value cell is a formula off 13_ListedMarks and 2_Assumptions — change an input there and this sheet reprices.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Holding</t>
   </si>
   <si>
@@ -589,13 +617,13 @@
     <t xml:space="preserve">Trojan Construction (51%)</t>
   </si>
   <si>
-    <t xml:space="preserve">ADQ named transaction: 49% sold FY2024 for AED 4,997mn (audited CF) → 100% ≈ 10.2bn</t>
+    <t xml:space="preserve">Buyer-outlay basis (ADH FY24 CF 4,997mn; ADQ-side ~5,043) → 100% ≈ 10.2bn; seller-note basis 7.27bn carried as the 9_Sensitivity stress</t>
   </si>
   <si>
     <t xml:space="preserve">Other / residual (attributable book)</t>
   </si>
   <si>
-    <t xml:space="preserve">Parent book 60.10 − est. carried book of the five marked stakes (est., Driver Ledger)</t>
+    <t xml:space="preserve">Parent book − est. carried book of the five marked stakes (est., Driver Ledger)</t>
   </si>
   <si>
     <t xml:space="preserve">GAV (attributable)</t>
@@ -682,6 +710,21 @@
     <t xml:space="preserve">25%</t>
   </si>
   <si>
+    <t xml:space="preserve">NAV/share: Trojan mark basis →</t>
+  </si>
+  <si>
+    <t xml:space="preserve">buyer-outlay 10.20bn (base)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seller-note 7.27bn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Par (0% discount)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15% discount (central)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Central FV: lens-weight stress</t>
   </si>
   <si>
@@ -892,6 +935,9 @@
     <t xml:space="preserve">ADH (wrapper)</t>
   </si>
   <si>
+    <t xml:space="preserve">Blue mcap &amp; stake cells are the SOTP input layer — 8_SOTP references them by formula.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Step-2A: per-driver gate and the Sweep Register</t>
   </si>
   <si>
@@ -976,7 +1022,7 @@
     <t xml:space="preserve">Trojan mark</t>
   </si>
   <si>
-    <t xml:space="preserve">ADQ transaction AED 4,997mn for 49% (audited FY24 CF)</t>
+    <t xml:space="preserve">ADQ 49% deal, buyer-outlay ≈5.0bn; seller-note 3,562 — dual-framed, 9_Sensitivity stress</t>
   </si>
   <si>
     <t xml:space="preserve">R4-06</t>
@@ -1180,10 +1226,13 @@
     <t xml:space="preserve">Stake change — NMDC</t>
   </si>
   <si>
-    <t xml:space="preserve">66.91%→76.68% during 2025; cash for added stakes 2.86bn; NCI acq. −5.10bn equity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY25 FS subsid. list + SOCIE</t>
+    <t xml:space="preserve">66.91%→76.68%: AD Ports 9.77% block (82.5mn sh) for AED 1.6bn, 27-Nov-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADH + AD Ports releases 27-Nov-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nov-25</t>
   </si>
   <si>
     <t xml:space="preserve">Stake change — NCTH</t>
@@ -1201,10 +1250,10 @@
     <t xml:space="preserve">Stake change — ADCH/ADQ</t>
   </si>
   <si>
-    <t xml:space="preserve">49% of Trojan Construction Holding sold to ADQ FY24 for AED 4,997mn; ADH keeps 51%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY24 audited CF; releases</t>
+    <t xml:space="preserve">49% to ADQ FY24: buyer-outlay ≈5.0bn (CF 4,997; ADQ-side ~5,043); seller-note 3,562+1,456 NCI — dual-framed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY24 FS (both sides); releases</t>
   </si>
   <si>
     <t xml:space="preserve">Dividend/buyback</t>
@@ -1348,22 +1397,115 @@
     <t xml:space="preserve">Expert 2</t>
   </si>
   <si>
-    <t xml:space="preserve">Look-through owner earnings (AED 7.8bn attrib.) × 7.5–10.5x quality-holdco multiple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attributable look-through earnings compound &gt;12% for 2 consecutive years</t>
+    <t xml:space="preserve">Accountant: justified P/B ((ROAE−g)/(Ke−g)) on the cleaned book — FVTPL stripped, ROAE 10.3%, BVPS 6.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FV gains convert to cash 2 consecutive quarters (→ reported-ROAE basis) or a borrowings note &gt;&gt;41.4bn (→ haircut row)</t>
   </si>
   <si>
     <t xml:space="preserve">Expert 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Flows/scenario tree: 35% scarcity-premium persists (spot+5%), 40% drift to NAV+5%, 25% de-rate to −25% NAV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free-float/index event (e.g., FTSE/MSCI weight change or IHC sell-down) resolves the premium either way</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panel span AED 6.3–7.1 vs weighted central 7.30 — all three land below spot 8.22.</t>
+    <t xml:space="preserve">Macro-Policy state tree: 35% easing+fiscal (8.20), 40% hold+DMTT glide (6.90), 25% war-fiscal stress (5.60)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durable ceasefire + Fed cutting → ~7.4; month-plus Hormuz closure or accelerated Pillar-Two top-ups → ~6.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panel span AED 6.3–7.0 vs weighted central 7.30 — all three land below spot 8.22.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-Share &amp; Ratios — the standardized dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formulas reference 4_IS / 5_BS / 2_Assumptions; FY25 valuation rows price the 3-Jul-26 spot.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPS — attributable (AED)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/d FY23 (attributable split not in MD&amp;A summary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPS (AED)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First distribution under the FY25 policy (20 fils, paid Q1-26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owners equity / 10.0bn sh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P/E (spot / EPS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3x on FY25 — the wrapper multiple of 13_ListedMarks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P/B (spot / BVPS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37x FY25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dividend yield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4% at spot; policy grows 5%/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FCF yield (CFO−capex / mcap)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY25 CFO 9.63 − capex 5.57 over mcap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV/EBITDA (adj.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV = mcap + net debt + hybrids; adj. EBITDA 17.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROAE — reported</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attributable NP / avg owners equity — 14.3% FY25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROAE — cleaned (ex-FVTPL, flagged)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strips ~70% of the +3.15bn FVTPL as parent-level (Appendix C.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROAIC (NOPAT / avg invested capital)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOPAT 12.9 / avg (total equity + net debt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5% FY25 held flat in the forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net margin — attributable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effective tax rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CT 9% + DMTT from 1-Jan-25; glide to 15% statutory in the DCF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net debt / adj. EBITDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.06x FY25 — the borrowings line is derived and flagged</t>
   </si>
 </sst>
 </file>
@@ -1537,84 +1679,88 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1873,76 +2019,76 @@
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="120"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="120"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1965,93 +2111,93 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="110"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="110"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>219</v>
+      <c r="A1" s="1" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>221</v>
+      <c r="A3" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>223</v>
+      <c r="A4" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>225</v>
+      <c r="A5" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>227</v>
+      <c r="A6" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>229</v>
+      <c r="A7" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>231</v>
+      <c r="A8" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>233</v>
+      <c r="A9" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>235</v>
+      <c r="A10" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>237</v>
+      <c r="A11" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>239</v>
+      <c r="A12" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -2073,237 +2219,237 @@
   <dimension ref="A1:D26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>240</v>
+      <c r="A1" s="1" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>244</v>
+      <c r="A3" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="B4" s="10" t="n">
+      <c r="A4" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="B4" s="9" t="n">
         <v>7.03606581913957</v>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="9" t="n">
         <v>6.3033355634558</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="17" t="n">
         <v>-0.233170856027275</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="B5" s="10" t="n">
+      <c r="A5" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="B5" s="9" t="n">
         <v>7.28533889855946</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="9" t="n">
         <v>6.69512674711483</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="17" t="n">
         <v>-0.185507694998196</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="B6" s="10" t="n">
+      <c r="A6" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="B6" s="9" t="n">
         <v>7.72799675780632</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="9" t="n">
         <v>7.41530548055432</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="17" t="n">
         <v>-0.0978947103948515</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="B7" s="10" t="n">
+      <c r="A7" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="B7" s="9" t="n">
         <v>8.2410031367216</v>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="9" t="n">
         <v>8.28850183295124</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="17" t="n">
         <v>0.00833355632010213</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="B8" s="10" t="n">
+      <c r="A8" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="B8" s="9" t="n">
         <v>8.79303429161134</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="9" t="n">
         <v>9.27359905323224</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="17" t="n">
         <v>0.128175067303192</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="B9" s="10" t="n">
+      <c r="A9" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="B9" s="9" t="n">
         <v>9.33236407229773</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="9" t="n">
         <v>10.280798854637</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="17" t="n">
         <v>0.250705456768495</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="B10" s="10" t="n">
+      <c r="A10" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="B10" s="9" t="n">
         <v>9.66667791768897</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="9" t="n">
         <v>10.9270330272989</v>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="17" t="n">
         <v>0.329322752712757</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>253</v>
+      <c r="A12" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="B13" s="15" t="n">
+      <c r="A13" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B13" s="14" t="n">
         <v>0.52122</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="B14" s="15" t="n">
+      <c r="A14" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B14" s="14" t="n">
         <v>0.30094</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B15" s="15" t="n">
+      <c r="A15" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B15" s="14" t="n">
         <v>0.45346</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="B16" s="15" t="n">
+      <c r="A16" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B16" s="14" t="n">
         <v>0.2456</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="B17" s="15" t="n">
+      <c r="A17" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B17" s="14" t="n">
         <v>0.082</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>260</v>
+      <c r="A19" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B20" s="15" t="n">
+      <c r="B20" s="14" t="n">
         <v>0.84526</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="n">
+      <c r="A21" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="B21" s="15" t="n">
+      <c r="B21" s="14" t="n">
         <v>0.72762</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B22" s="15" t="n">
+      <c r="B22" s="14" t="n">
         <v>0.58598</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="n">
+      <c r="A23" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="B23" s="15" t="n">
+      <c r="B23" s="14" t="n">
         <v>0.43936</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="n">
+      <c r="A24" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B24" s="15" t="n">
+      <c r="B24" s="14" t="n">
         <v>0.31024</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10" t="n">
+      <c r="A25" s="9" t="n">
         <v>9.5</v>
       </c>
-      <c r="B25" s="15" t="n">
+      <c r="B25" s="14" t="n">
         <v>0.2087</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B26" s="15" t="n">
+      <c r="B26" s="14" t="n">
         <v>0.132</v>
       </c>
     </row>
@@ -2326,120 +2472,120 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>261</v>
+      <c r="A1" s="1" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>266</v>
+      <c r="A3" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="B4" s="12" t="n">
+      <c r="A4" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="B4" s="11" t="n">
         <v>18.1</v>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="11" t="n">
         <v>27.8</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="11" t="n">
         <v>5.2</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="11" t="n">
         <v>81.4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="B5" s="12" t="n">
+      <c r="A5" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="B5" s="11" t="n">
         <v>26.3</v>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C5" s="11" t="n">
         <v>28.8</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="11" t="n">
         <v>38.8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="B6" s="12" t="n">
+      <c r="A6" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="B6" s="11" t="n">
         <v>11.8</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="11" t="n">
         <v>13.1</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="11" t="n">
         <v>0.9</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="11" t="n">
         <v>12.6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="B7" s="12" t="n">
+      <c r="A7" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B7" s="11" t="n">
         <v>7.2</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="11" t="n">
         <v>9.1</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="11" t="n">
         <v>4.4</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="11" t="n">
         <v>44.7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="B8" s="12" t="n">
+      <c r="A8" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="B8" s="11" t="n">
         <v>63.4</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="11" t="n">
         <v>78.8</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="11" t="n">
         <v>13.5</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="11" t="n">
         <v>177.5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>272</v>
+      <c r="A10" s="12" t="s">
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -2458,157 +2604,162 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>273</v>
+      <c r="A1" s="1" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>280</v>
+      <c r="A3" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="B4" s="10" t="n">
+      <c r="A4" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="B4" s="7" t="n">
         <v>64.87</v>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="9" t="n">
         <v>7.51</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="9" t="n">
         <v>1.85</v>
       </c>
-      <c r="F4" s="15" t="n">
+      <c r="F4" s="18" t="n">
         <v>0.3163</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="9" t="n">
         <v>2.38</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="B5" s="10" t="n">
+      <c r="A5" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="B5" s="7" t="n">
         <v>18.79</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="9" t="n">
         <v>3.62</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>5.2</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="9" t="n">
         <v>1.63</v>
       </c>
-      <c r="F5" s="15" t="n">
+      <c r="F5" s="18" t="n">
         <v>0.7668</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="9" t="n">
         <v>2.78</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="B6" s="10" t="n">
+      <c r="A6" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="B6" s="7" t="n">
         <v>24.56</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="9" t="n">
         <v>0.94</v>
       </c>
-      <c r="F6" s="15" t="n">
+      <c r="F6" s="18" t="n">
         <v>0.3506</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="9" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="B7" s="10" t="n">
+      <c r="A7" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" s="7" t="n">
         <v>3.27</v>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="9" t="n">
         <v>1.09</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="F7" s="18" t="n">
         <v>0.7373</v>
       </c>
-      <c r="G7" s="10" t="n">
+      <c r="G7" s="9" t="n">
         <v>0.22</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="B8" s="10" t="n">
+      <c r="A8" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="B8" s="9" t="n">
         <v>82.2</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="9" t="n">
         <v>8.01</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>10.3</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="9" t="n">
         <v>1.37</v>
       </c>
-      <c r="F8" s="15" t="n">
+      <c r="F8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="9" t="n">
         <v>8.01</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19" t="s">
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -2630,633 +2781,633 @@
   <dimension ref="A1:F38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>285</v>
+      <c r="A1" s="1" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>289</v>
+      <c r="A3" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>293</v>
+      <c r="A4" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>296</v>
+      <c r="A5" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="F22" s="4" t="s">
+      <c r="C34" s="3" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="E27" s="4" t="s">
+      <c r="D34" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>403</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>107</v>
+      <c r="D38" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -3278,162 +3429,162 @@
   <dimension ref="A1:L12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="4" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="4" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>408</v>
+      <c r="A1" s="1" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>409</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>410</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>412</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>413</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>414</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>415</v>
+      <c r="A3" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="C4" s="4" t="n">
+      <c r="A4" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="9" t="n">
         <v>8.22</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="9" t="n">
         <v>7.03606581913957</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="9" t="n">
         <v>7.72799675780632</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="9" t="n">
         <v>8.2410031367216</v>
       </c>
-      <c r="H4" s="10" t="n">
+      <c r="H4" s="9" t="n">
         <v>8.79303429161134</v>
       </c>
-      <c r="I4" s="10" t="n">
+      <c r="I4" s="9" t="n">
         <v>9.66667791768897</v>
       </c>
-      <c r="J4" s="10" t="n">
+      <c r="J4" s="9" t="n">
         <v>0.3413</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>419</v>
+      <c r="K4" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="C5" s="4" t="n">
+      <c r="A5" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>8.22</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="9" t="n">
         <v>6.3033355634558</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="9" t="n">
         <v>7.41530548055432</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="9" t="n">
         <v>8.28850183295124</v>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H5" s="9" t="n">
         <v>9.27359905323224</v>
       </c>
-      <c r="I5" s="10" t="n">
+      <c r="I5" s="9" t="n">
         <v>10.9270330272989</v>
       </c>
-      <c r="J5" s="10" t="n">
+      <c r="J5" s="9" t="n">
         <v>0.3413</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>419</v>
+      <c r="K5" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>420</v>
+      <c r="A7" s="6" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>421</v>
+      <c r="A8" s="3" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>422</v>
+      <c r="A9" s="3" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>423</v>
+      <c r="A10" s="3" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>424</v>
+      <c r="A11" s="3" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>425</v>
+      <c r="A12" s="3" t="s">
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -3455,96 +3606,446 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="60"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>426</v>
+      <c r="A1" s="1" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>428</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>430</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>431</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>432</v>
+      <c r="A3" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="C4" s="10" t="n">
+      <c r="A4" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C4" s="9" t="n">
         <v>5.2</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>435</v>
+      <c r="F4" s="3" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="C5" s="10" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="D5" s="10" t="n">
+      <c r="A5" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D6" s="9" t="n">
         <v>7.03</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E6" s="9" t="n">
         <v>8.2</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>438</v>
+      <c r="F6" s="3" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="s">
+        <v>458</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="66"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="B4" s="9" t="str">
+        <f aca="false">4_IS!B12</f>
+        <v>n/d</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <f aca="false">4_IS!C12</f>
+        <v>0.88</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <f aca="false">4_IS!D12</f>
+        <v>0.79</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>439</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="10" t="n">
-        <v>7.07</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4" t="s">
-        <v>441</v>
+      <c r="A6" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <f aca="false">5_BS!B19</f>
+        <v>4.2</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <f aca="false">5_BS!C19</f>
+        <v>5.23</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <f aca="false">5_BS!D19</f>
+        <v>6.01</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <f aca="false">2_Assumptions!B4/4_IS!C12</f>
+        <v>9.34090909090909</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <f aca="false">2_Assumptions!B4/4_IS!D12</f>
+        <v>10.4050632911392</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>442</v>
+      <c r="A8" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <f aca="false">2_Assumptions!B4/5_BS!B19</f>
+        <v>1.95714285714286</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <f aca="false">2_Assumptions!B4/5_BS!C19</f>
+        <v>1.5717017208413</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <f aca="false">2_Assumptions!B4/5_BS!D19</f>
+        <v>1.36772046589018</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <f aca="false">0.2/2_Assumptions!B4</f>
+        <v>0.024330900243309</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <f aca="false">(9.63-5.567)/(2_Assumptions!B4*2_Assumptions!B5)</f>
+        <v>0.0494282238442822</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <f aca="false">(2_Assumptions!B4*2_Assumptions!B5+5_BS!D18+1.816)/4_IS!D6</f>
+        <v>4.81107344632768</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <f aca="false">(4_IS!C11)/((5_BS!B12+5_BS!C12)/2)</f>
+        <v>0.188532762021933</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <f aca="false">(4_IS!D11)/((5_BS!C12+5_BS!D12)/2)</f>
+        <v>0.142620704383264</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <f aca="false">4_IS!D9/((5_BS!C15+5_BS!C18+5_BS!D15+5_BS!D18)/2)</f>
+        <v>0.129772144258337</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="B15" s="14" t="n">
+        <f aca="false">4_IS!B5/4_IS!B4</f>
+        <v>0.204845814977974</v>
+      </c>
+      <c r="C15" s="14" t="n">
+        <f aca="false">4_IS!C5/4_IS!C4</f>
+        <v>0.211937661682125</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <f aca="false">4_IS!D5/4_IS!D4</f>
+        <v>0.238387813392574</v>
+      </c>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B16" s="14" t="n">
+        <f aca="false">4_IS!B6/4_IS!B4</f>
+        <v>0.363436123348018</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <f aca="false">4_IS!C6/4_IS!C4</f>
+        <v>0.214524575683008</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <f aca="false">4_IS!D6/4_IS!D4</f>
+        <v>0.224690574420819</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <f aca="false">4_IS!C11/4_IS!C4</f>
+        <v>0.14019811975519</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <f aca="false">4_IS!D11/4_IS!D4</f>
+        <v>0.101732783243415</v>
+      </c>
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <f aca="false">5_BS!C18/4_IS!C6</f>
+        <v>0.0955882352941177</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <f aca="false">5_BS!D18/4_IS!D6</f>
+        <v>0.064406779661017</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -3563,385 +4064,441 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="110"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="110"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="7" t="n">
         <v>8.22</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="7" t="n">
         <v>78.775</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="7" t="n">
         <v>17.7</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="7" t="n">
         <v>0.2247</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="7" t="n">
         <v>0.09</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="7" t="n">
         <v>0.041</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="7" t="n">
         <v>0.065</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="7" t="n">
         <v>0.45</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="7" t="n">
         <v>0.12</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="7" t="n">
         <v>0.0475</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="8" t="n">
+      <c r="B15" s="7" t="n">
         <v>0.0487</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B16" s="7" t="n">
         <v>0.0493</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="8" t="n">
+      <c r="B17" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="8" t="n">
+      <c r="B18" s="7" t="n">
         <v>0.06</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B19" s="7" t="n">
         <v>41.4</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B20" s="8" t="n">
+      <c r="B20" s="7" t="n">
         <v>40.259</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B21" s="8" t="n">
+      <c r="B21" s="7" t="n">
         <v>0.03</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B22" s="8" t="n">
+      <c r="B22" s="7" t="n">
+        <v>60.096</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>36.84</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26" s="7" t="n">
         <v>0.15</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C26" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B23" s="8" t="n">
+      <c r="D26" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="7" t="n">
         <v>0.0393</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C27" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B24" s="8" t="n">
+      <c r="D27" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C28" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B26" s="8" t="n">
+      <c r="D28" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" s="7" t="n">
         <v>0.85</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C30" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B27" s="8" t="n">
+      <c r="D30" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="7" t="n">
         <v>9.5</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C31" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B28" s="8" t="n">
+      <c r="D31" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B32" s="7" t="n">
         <v>0.21</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>82</v>
+      <c r="D32" s="3" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -3963,234 +4520,234 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>83</v>
+      <c r="A1" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>88</v>
+      <c r="A3" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B4" s="10" t="n">
+      <c r="A4" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="9" t="n">
         <v>45.4</v>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="9" t="n">
         <v>63.396</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="9" t="n">
         <v>78.775</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="9" t="n">
         <v>18.79</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="B5" s="10" t="n">
+      <c r="A5" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="9" t="n">
         <v>16.5</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="9" t="n">
         <v>13.6</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="9" t="n">
         <v>4.3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B6" s="10" t="n">
+      <c r="A6" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="9" t="n">
         <v>13.514</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>15.032</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="9" t="n">
         <v>3.8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="10" t="n">
+      <c r="A7" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="9" t="n">
         <v>8.888</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="9" t="n">
         <v>8.014</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>93</v>
+      <c r="E7" s="3" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" s="10" t="n">
+      <c r="A8" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="9" t="n">
         <v>0.88</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>0.79</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>93</v>
+      <c r="E8" s="3" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="B9" s="10" t="n">
+      <c r="A9" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="9" t="n">
         <v>140.4</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="9" t="n">
         <v>177.519</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="9" t="n">
         <v>214.422</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="9" t="n">
         <v>225.8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B10" s="10" t="n">
+      <c r="A10" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="9" t="n">
         <v>52.286</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="9" t="n">
         <v>60.096</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>97</v>
+      <c r="E10" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="B11" s="10" t="n">
+      <c r="A11" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" s="9" t="n">
         <v>32.1</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="9" t="n">
         <v>38.227</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="9" t="n">
         <v>42.13</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>97</v>
+      <c r="E11" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B12" s="10" t="n">
+      <c r="A12" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="9" t="n">
         <v>30.1</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>97</v>
+      <c r="E12" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B13" s="10" t="n">
+      <c r="A13" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="9" t="n">
         <v>28.78</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="9" t="n">
         <v>40.259</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>97</v>
+      <c r="E13" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B14" s="10" t="n">
+      <c r="A14" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="9" t="n">
         <v>3.98</v>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="9" t="n">
         <v>1.14</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>97</v>
+      <c r="E14" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B15" s="4" t="n">
+      <c r="A15" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>97</v>
+      <c r="E15" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -4212,302 +4769,302 @@
   <dimension ref="A1:I12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="2" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="2" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>103</v>
+      <c r="A1" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>63.396</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>78.775</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>85.9</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>110.4</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" s="11" t="n">
+        <v>9.3</v>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>13.436</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>18.779</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B4" s="11" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="C4" s="11" t="n">
-        <v>63.396</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>78.775</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>85.9</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="G4" s="11" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="H4" s="11" t="n">
-        <v>105.2</v>
-      </c>
-      <c r="I4" s="11" t="n">
-        <v>110.4</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B5" s="12" t="n">
-        <v>9.3</v>
-      </c>
-      <c r="C5" s="12" t="n">
-        <v>13.436</v>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>18.779</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="F5" s="12" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="H5" s="12" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="I5" s="12" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="B6" s="11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="E6" s="11" t="n">
+      <c r="F7" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H8" s="11" t="n">
         <v>19.3</v>
       </c>
-      <c r="F6" s="11" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="H6" s="11" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="I6" s="11" t="n">
-        <v>24.8</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B7" s="12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="C7" s="12" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B8" s="12" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="C8" s="12" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="D8" s="12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="E8" s="12" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="H8" s="12" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="I8" s="12" t="n">
+      <c r="I8" s="11" t="n">
         <v>20.3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D9" s="12" t="n">
+      <c r="A9" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="11" t="n">
         <v>12.9</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="11" t="n">
         <v>13.9</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="F9" s="11" t="n">
         <v>14.8</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="G9" s="11" t="n">
         <v>15.7</v>
       </c>
-      <c r="H9" s="12" t="n">
+      <c r="H9" s="11" t="n">
         <v>16.4</v>
       </c>
-      <c r="I9" s="12" t="n">
+      <c r="I9" s="11" t="n">
         <v>17.2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B10" s="11" t="n">
+      <c r="A10" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="10" t="n">
         <v>13.3</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="10" t="n">
         <v>13.514</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="10" t="n">
         <v>15.032</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>97</v>
+      <c r="E10" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" s="11" t="n">
+      <c r="A11" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="10" t="n">
         <v>8.888</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="10" t="n">
         <v>8.014</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="10" t="n">
         <v>7.5</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="G11" s="10" t="n">
         <v>7.9</v>
       </c>
-      <c r="H11" s="11" t="n">
+      <c r="H11" s="10" t="n">
         <v>8.3</v>
       </c>
-      <c r="I11" s="11" t="n">
+      <c r="I11" s="10" t="n">
         <v>8.7</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="12" t="n">
+      <c r="A12" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="11" t="n">
         <v>0.88</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="11" t="n">
         <v>0.79</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="11" t="n">
         <v>0.7</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="11" t="n">
         <v>0.75</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" s="11" t="n">
         <v>0.79</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="H12" s="11" t="n">
         <v>0.83</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="I12" s="11" t="n">
         <v>0.87</v>
       </c>
     </row>
@@ -4530,250 +5087,250 @@
   <dimension ref="A1:D19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>118</v>
+      <c r="A1" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>66.9</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>71.723</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>81.342</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>24.779</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>29.309</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>18.336</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>17.415</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>105.796</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>133.079</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>28.78</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>40.259</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>12.541</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>19.671</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>26.307</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>34.796</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>140.4</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>177.519</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>214.422</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="B4" s="10" t="n">
-        <v>66.9</v>
-      </c>
-      <c r="C4" s="10" t="n">
-        <v>71.723</v>
-      </c>
-      <c r="D4" s="10" t="n">
-        <v>81.342</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="10" t="n">
-        <v>24.779</v>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>29.309</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="10" t="n">
-        <v>18.336</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>17.415</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="B7" s="10" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="C7" s="10" t="n">
-        <v>105.796</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>133.079</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B8" s="10" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>28.78</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>40.259</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" s="10" t="n">
-        <v>12.541</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>19.671</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>26.307</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>34.796</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B11" s="10" t="n">
-        <v>140.4</v>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>177.519</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>214.422</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="9" t="n">
         <v>52.286</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="9" t="n">
         <v>60.096</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B13" s="10" t="n">
+      <c r="A13" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B13" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="9" t="n">
         <v>1.816</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="9" t="n">
         <v>1.816</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="B14" s="10" t="n">
+      <c r="A14" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B14" s="9" t="n">
         <v>32.1</v>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="9" t="n">
         <v>38.227</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="9" t="n">
         <v>42.13</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="B15" s="10" t="n">
+      <c r="A15" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B15" s="9" t="n">
         <v>75.9</v>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C15" s="9" t="n">
         <v>92.328</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="9" t="n">
         <v>104.042</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="B16" s="10" t="n">
+      <c r="A16" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B16" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C16" s="9" t="n">
         <v>85.192</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="9" t="n">
         <v>110.379</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B17" s="10" t="n">
+      <c r="A17" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B17" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="C17" s="10" t="n">
+      <c r="C17" s="9" t="n">
         <v>30.1</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="9" t="n">
         <v>41.4</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B18" s="10" t="n">
+      <c r="A18" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" s="9" t="n">
         <v>3.98</v>
       </c>
-      <c r="C18" s="10" t="n">
+      <c r="C18" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="9" t="n">
         <v>1.14</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="B19" s="10" t="n">
+      <c r="A19" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B19" s="9" t="n">
         <v>4.2</v>
       </c>
-      <c r="C19" s="10" t="n">
+      <c r="C19" s="9" t="n">
         <v>5.23</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="9" t="n">
         <v>6.01</v>
       </c>
     </row>
@@ -4796,128 +5353,128 @@
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>133</v>
+      <c r="A1" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>87</v>
+      <c r="A3" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="B4" s="10" t="n">
+      <c r="A4" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" s="9" t="n">
         <v>10.301</v>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="9" t="n">
         <v>9.63</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B5" s="10" t="n">
+      <c r="A5" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="9" t="n">
         <v>4.879</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="9" t="n">
         <v>5.567</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="B6" s="10" t="n">
+      <c r="A6" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" s="9" t="n">
         <v>5.423</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="9" t="n">
         <v>4.063</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="B7" s="10" t="n">
+      <c r="A7" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" s="9" t="n">
         <v>-2.326</v>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="9" t="n">
         <v>-7.47</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="10" t="n">
+      <c r="A8" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="9" t="n">
         <v>8.6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B9" s="10" t="n">
+      <c r="A9" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="B10" s="10" t="n">
+      <c r="A10" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10" s="9" t="n">
         <v>2.056</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="9" t="n">
         <v>1.593</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="B11" s="10" t="n">
+      <c r="A11" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="9" t="n">
         <v>4.989</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="9" t="n">
         <v>8.332</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="10" t="n">
+      <c r="A12" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="9" t="n">
         <v>-0.143</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
-        <v>143</v>
+      <c r="A14" s="12" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -4939,369 +5496,369 @@
   <dimension ref="A1:F29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>144</v>
+      <c r="A1" s="1" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
-        <v>145</v>
+      <c r="A2" s="4" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="F3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>112</v>
       </c>
+      <c r="B3" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B4" s="12" t="n">
+      <c r="A4" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" s="11" t="n">
         <v>85.865</v>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="11" t="n">
         <v>92.734</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="11" t="n">
         <v>99.225</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="11" t="n">
         <v>105.179</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="11" t="n">
         <v>110.438</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B5" s="12" t="n">
+      <c r="A5" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5" s="11" t="n">
         <v>19.293</v>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C5" s="11" t="n">
         <v>20.836</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="11" t="n">
         <v>22.295</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="11" t="n">
         <v>23.633</v>
       </c>
-      <c r="F5" s="12" t="n">
+      <c r="F5" s="11" t="n">
         <v>24.814</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" s="12" t="n">
+      <c r="A6" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" s="11" t="n">
         <v>3.52</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="11" t="n">
         <v>3.802</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="11" t="n">
         <v>4.068</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="11" t="n">
         <v>4.312</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="11" t="n">
         <v>4.528</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="B7" s="12" t="n">
+      <c r="A7" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B7" s="11" t="n">
         <v>15.773</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="11" t="n">
         <v>17.034</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="11" t="n">
         <v>18.227</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="11" t="n">
         <v>19.32</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="11" t="n">
         <v>20.286</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B8" s="12" t="n">
+      <c r="A8" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="11" t="n">
         <v>13.88</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="11" t="n">
         <v>14.82</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="11" t="n">
         <v>15.675</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="11" t="n">
         <v>16.422</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="11" t="n">
         <v>17.243</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B9" s="12" t="n">
+      <c r="A9" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B9" s="11" t="n">
         <v>3.52</v>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="11" t="n">
         <v>3.802</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="11" t="n">
         <v>4.068</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="11" t="n">
         <v>4.312</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="F9" s="11" t="n">
         <v>4.528</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B10" s="12" t="n">
+      <c r="A10" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B10" s="11" t="n">
         <v>5.581</v>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="11" t="n">
         <v>5.842</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="11" t="n">
         <v>5.954</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="11" t="n">
         <v>6.1</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="11" t="n">
         <v>6.074</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="B11" s="12" t="n">
+      <c r="A11" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B11" s="11" t="n">
         <v>3.19</v>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="11" t="n">
         <v>2.61</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="11" t="n">
         <v>1.947</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="11" t="n">
         <v>1.488</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="11" t="n">
         <v>1.052</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="B12" s="12" t="n">
+      <c r="A12" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B12" s="11" t="n">
         <v>8.629</v>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="11" t="n">
         <v>10.169</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="11" t="n">
         <v>11.842</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="11" t="n">
         <v>13.146</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="11" t="n">
         <v>14.646</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B13" s="14" t="n">
+      <c r="A13" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B13" s="13" t="n">
         <v>0.921</v>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="13" t="n">
         <v>0.848</v>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="13" t="n">
         <v>0.78</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="13" t="n">
         <v>0.719</v>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="13" t="n">
         <v>0.662</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="B14" s="12" t="n">
+      <c r="A14" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B14" s="11" t="n">
         <v>7.944</v>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="11" t="n">
         <v>8.62</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="D14" s="11" t="n">
         <v>9.242</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="11" t="n">
         <v>9.446</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="F14" s="11" t="n">
         <v>9.689</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="B16" s="12" t="n">
+      <c r="A16" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B16" s="11" t="n">
         <v>268.7</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="B17" s="12" t="n">
+      <c r="A17" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B17" s="11" t="n">
         <v>177.7</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="B18" s="12" t="n">
+      <c r="A18" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B18" s="11" t="n">
         <v>222.7</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="B19" s="15" t="n">
+      <c r="A19" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B19" s="14" t="n">
         <v>0.798</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="B20" s="10" t="n">
+      <c r="A20" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B20" s="9" t="n">
         <v>1.1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="B21" s="10" t="n">
+      <c r="A21" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B21" s="9" t="n">
         <v>1.816</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="B22" s="12" t="n">
+      <c r="A22" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B22" s="11" t="n">
         <v>219.8</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="B23" s="15" t="n">
+      <c r="A23" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B23" s="14" t="n">
         <v>0.5331</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="B24" s="12" t="n">
+      <c r="A24" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B24" s="11" t="n">
         <v>117.2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="B25" s="10" t="n">
+      <c r="A25" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="B25" s="9" t="n">
         <v>11.72</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="B26" s="15" t="n">
+      <c r="A26" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B26" s="14" t="n">
         <v>0.0861</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="B27" s="15" t="n">
+      <c r="A27" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B27" s="14" t="n">
         <v>0.0962</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="B28" s="15" t="n">
+      <c r="A28" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="B28" s="14" t="n">
         <v>0.0968</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="B29" s="15" t="n">
+      <c r="A29" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B29" s="14" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -5324,181 +5881,208 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="80"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="80"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>169</v>
+      <c r="A1" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>174</v>
+      <c r="A3" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="B4" s="15" t="n">
+      <c r="A4" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="14" t="n">
+        <f aca="false">13_ListedMarks!F4</f>
         <v>0.3163</v>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="11" t="n">
+        <f aca="false">13_ListedMarks!B4</f>
         <v>64.87</v>
       </c>
-      <c r="D4" s="12" t="n">
-        <v>20.52</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>176</v>
+      <c r="D4" s="11" t="n">
+        <f aca="false">C4*B4</f>
+        <v>20.518381</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="B5" s="15" t="n">
+      <c r="A5" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" s="14" t="n">
+        <f aca="false">13_ListedMarks!F5</f>
         <v>0.7668</v>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C5" s="11" t="n">
+        <f aca="false">13_ListedMarks!B5</f>
         <v>18.79</v>
       </c>
-      <c r="D5" s="12" t="n">
-        <v>14.41</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>178</v>
+      <c r="D5" s="11" t="n">
+        <f aca="false">C5*B5</f>
+        <v>14.408172</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="B6" s="15" t="n">
+      <c r="A6" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B6" s="14" t="n">
+        <f aca="false">13_ListedMarks!F6</f>
         <v>0.3506</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="11" t="n">
+        <f aca="false">13_ListedMarks!B6</f>
         <v>24.56</v>
       </c>
-      <c r="D6" s="12" t="n">
-        <v>8.61</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>180</v>
+      <c r="D6" s="11" t="n">
+        <f aca="false">C6*B6</f>
+        <v>8.610736</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="B7" s="15" t="n">
+      <c r="A7" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" s="14" t="n">
+        <f aca="false">13_ListedMarks!F7</f>
         <v>0.7373</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="11" t="n">
+        <f aca="false">13_ListedMarks!B7</f>
         <v>3.27</v>
       </c>
-      <c r="D7" s="12" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>182</v>
+      <c r="D7" s="11" t="n">
+        <f aca="false">C7*B7</f>
+        <v>2.410971</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="B8" s="15" t="n">
+      <c r="A8" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B8" s="14" t="n">
         <v>0.51</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="11" t="n">
+        <f aca="false">2_Assumptions!B24</f>
         <v>10.2</v>
       </c>
-      <c r="D8" s="12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>184</v>
+      <c r="D8" s="11" t="n">
+        <f aca="false">C8*B8</f>
+        <v>5.202</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>23.26</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>186</v>
+      <c r="A9" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <f aca="false">2_Assumptions!B22-2_Assumptions!B23</f>
+        <v>23.256</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>74.4</v>
+      <c r="A10" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <f aca="false">SUM(D4:D9)</f>
+        <v>74.40626</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>190</v>
+      <c r="A12" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B13" s="12" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="C13" s="10" t="n">
-        <v>5.58</v>
+      <c r="A13" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B13" s="11" t="n">
+        <f aca="false">D10*(1-0.25)</f>
+        <v>55.804695</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <f aca="false">B13/2_Assumptions!B5</f>
+        <v>5.5804695</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B14" s="12" t="n">
-        <v>63.24</v>
-      </c>
-      <c r="C14" s="17" t="n">
-        <v>6.32</v>
+      <c r="A14" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B14" s="11" t="n">
+        <f aca="false">D10*(1-0.15)</f>
+        <v>63.245321</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <f aca="false">B14/2_Assumptions!B5</f>
+        <v>6.3245321</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="B15" s="12" t="n">
-        <v>74.4</v>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>7.44</v>
+      <c r="A15" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B15" s="11" t="n">
+        <f aca="false">D10*(1-0)</f>
+        <v>74.40626</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <f aca="false">B15/2_Assumptions!B5</f>
+        <v>7.440626</v>
       </c>
     </row>
   </sheetData>
@@ -5517,247 +6101,280 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>194</v>
+      <c r="A1" s="1" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>200</v>
+      <c r="A3" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="B4" s="10" t="n">
+      <c r="A4" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B4" s="9" t="n">
         <v>11.73</v>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="9" t="n">
         <v>12.67</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="9" t="n">
         <v>13.81</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="9" t="n">
         <v>15.21</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="9" t="n">
         <v>16.98</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="B5" s="10" t="n">
+      <c r="A5" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="B5" s="9" t="n">
         <v>10.93</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="9" t="n">
         <v>11.74</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>12.7</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="9" t="n">
         <v>13.86</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="9" t="n">
         <v>15.31</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="B6" s="10" t="n">
+      <c r="A6" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="B6" s="9" t="n">
         <v>10.23</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="9" t="n">
         <v>10.93</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>11.75</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="9" t="n">
         <v>12.73</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="9" t="n">
         <v>13.93</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="B7" s="10" t="n">
+      <c r="A7" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B7" s="9" t="n">
         <v>9.61</v>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="9" t="n">
         <v>10.22</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="9" t="n">
         <v>10.93</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="9" t="n">
         <v>11.76</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="F7" s="9" t="n">
         <v>12.77</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="B8" s="10" t="n">
+      <c r="A8" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B8" s="9" t="n">
         <v>8.93</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="9" t="n">
         <v>9.44</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>10.04</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="9" t="n">
         <v>10.74</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="9" t="n">
         <v>11.56</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>209</v>
+      <c r="A11" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B12" s="10" t="n">
+      <c r="A12" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B12" s="9" t="n">
         <v>6.94</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="9" t="n">
         <v>7.44</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="9" t="n">
         <v>7.94</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="B13" s="10" t="n">
+      <c r="A13" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B13" s="9" t="n">
         <v>6.246</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="9" t="n">
         <v>6.696</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="9" t="n">
         <v>7.146</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="B14" s="10" t="n">
+      <c r="A14" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="B14" s="9" t="n">
         <v>5.899</v>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="9" t="n">
         <v>6.324</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="9" t="n">
         <v>6.749</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="B15" s="10" t="n">
+      <c r="A15" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B15" s="9" t="n">
         <v>5.552</v>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C15" s="9" t="n">
         <v>5.952</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="9" t="n">
         <v>6.352</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B16" s="10" t="n">
+      <c r="A16" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B16" s="9" t="n">
         <v>5.205</v>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C16" s="9" t="n">
         <v>5.58</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="9" t="n">
         <v>5.955</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D18" s="6" t="s">
+      <c r="A18" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>7.29</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="B19" s="10" t="n">
+      <c r="D22" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B23" s="9" t="n">
         <v>6.08</v>
       </c>
-      <c r="C19" s="10" t="n">
+      <c r="C23" s="9" t="n">
         <v>7.3</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D23" s="9" t="n">
         <v>8.82</v>
       </c>
     </row>

--- a/files/ALPHADHABI_Valuation_Model_10-07-2026_public.xlsx
+++ b/files/ALPHADHABI_Valuation_Model_10-07-2026_public.xlsx
@@ -68,7 +68,7 @@
     <t xml:space="preserve">Weighted central (12-mo, risk-adjusted)</t>
   </si>
   <si>
-    <t xml:space="preserve">AED 7.30  (range 6.08–8.82)</t>
+    <t xml:space="preserve">AED 7.13  (range 5.95–8.63)</t>
   </si>
   <si>
     <t xml:space="preserve">60-day MC band (5–95%)</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">high</t>
   </si>
   <si>
-    <t xml:space="preserve">Published weights 45/15/25/15</t>
+    <t xml:space="preserve">Published weights 55/15/15/15</t>
   </si>
   <si>
     <t xml:space="preserve">Monte Carlo engine — v3 carry-anchored YZ-HAR-t, AE provisional fit</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">Durable ceasefire + Fed cutting → ~7.4; month-plus Hormuz closure or accelerated Pillar-Two top-ups → ~6.4</t>
   </si>
   <si>
-    <t xml:space="preserve">Panel span AED 6.3–7.0 vs weighted central 7.30 — all three land below spot 8.22.</t>
+    <t xml:space="preserve">Panel span AED 6.3–7.0 vs weighted central 7.13 — all three land below spot 8.22.</t>
   </si>
   <si>
     <t xml:space="preserve">Per-Share &amp; Ratios — the standardized dashboard</t>
@@ -6369,13 +6369,13 @@
         <v>232</v>
       </c>
       <c r="B23" s="9" t="n">
-        <v>6.08</v>
+        <v>5.95</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>7.3</v>
+        <v>7.13</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>8.82</v>
+        <v>8.63</v>
       </c>
     </row>
   </sheetData>
